--- a/Results/Study 1/Confusion Matrices (validation images).xlsx
+++ b/Results/Study 1/Confusion Matrices (validation images).xlsx
@@ -410,21 +410,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>99</v>
-      </c>
-      <c r="C2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>85</v>
+        <v>118</v>
+      </c>
+      <c r="C2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -450,21 +450,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>126</v>
-      </c>
-      <c r="C2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>63</v>
-      </c>
-      <c r="C3">
-        <v>97</v>
+        <v>123</v>
+      </c>
+      <c r="C2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -530,21 +530,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>107</v>
-      </c>
-      <c r="C2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>63</v>
-      </c>
-      <c r="C3">
-        <v>97</v>
+        <v>138</v>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -570,21 +570,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>154</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>68</v>
-      </c>
-      <c r="C3">
-        <v>92</v>
+        <v>96</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -610,10 +610,130 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>112</v>
-      </c>
-      <c r="C2">
-        <v>48</v>
+        <v>119</v>
+      </c>
+      <c r="C2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>113</v>
+      </c>
+      <c r="C2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>40</v>
+      </c>
+      <c r="C3">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>95</v>
+      </c>
+      <c r="C2">
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -632,126 +752,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>99</v>
-      </c>
-      <c r="C2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>119</v>
-      </c>
-      <c r="C2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>48</v>
-      </c>
-      <c r="C3">
-        <v>112</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>141</v>
-      </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>99</v>
-      </c>
-      <c r="C3">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
@@ -770,21 +770,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>136</v>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>58</v>
-      </c>
-      <c r="C3">
-        <v>102</v>
+        <v>130</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -810,21 +810,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>55</v>
-      </c>
-      <c r="C2">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>34</v>
-      </c>
-      <c r="C3">
-        <v>126</v>
+        <v>96</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -850,21 +850,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>48</v>
-      </c>
-      <c r="C2">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>48</v>
-      </c>
-      <c r="C3">
-        <v>112</v>
+        <v>64</v>
+      </c>
+      <c r="C2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>64</v>
+      </c>
+      <c r="C3">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
